--- a/individual_details.xlsx
+++ b/individual_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\css6\Dropbox\A\ASQ\sutherlandecology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A173C8-CCC3-4D81-9EA7-9C2ACD463C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F012FEE8-8C78-4E26-AA92-E83A39CD3A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DEC350D0-BA79-4816-9F19-79808F91A9D5}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="157">
   <si>
     <t>Name</t>
   </si>
@@ -450,9 +449,6 @@
     <t>Spatial population ecology of the Diamondback Terrapin at their northern range limit</t>
   </si>
   <si>
-    <t>How do recreational activities alter spatiotemporal species interactions networks, and can this knowledge assist in promoting pro-environmental behaviour?</t>
-  </si>
-  <si>
     <t>Senior Lecturer, Harper Adams University</t>
   </si>
   <si>
@@ -505,6 +501,36 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/rekha-mohan-239492319/</t>
+  </si>
+  <si>
+    <t>cowans.jpg</t>
+  </si>
+  <si>
+    <t>How can conservation technology advance our understanding of recreational disturbance effects on wildlife, and how can pro-environmental behaviour be encouraged in outdoor recreationists?</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/amber-cowans/</t>
+  </si>
+  <si>
+    <t>https://ac-ecology.github.io/amber-cowans.website/</t>
+  </si>
+  <si>
+    <t>https://x.com/AmberCowans</t>
+  </si>
+  <si>
+    <t>Gonçalo Curveira-Santos</t>
+  </si>
+  <si>
+    <t>Researcher, CIBIO (Research Centre in Biodiversity and Genetic Resources)</t>
+  </si>
+  <si>
+    <t>Responses of carnivore assemblages to conservation and management models in South Africa</t>
+  </si>
+  <si>
+    <t>https://www.cibio.up.pt/en/people/details/goncalo-curveira-santos/details/</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/profile/Goncalo-Curveira-Santos</t>
   </si>
 </sst>
 </file>
@@ -924,15 +950,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562D1C5D-4376-4368-B05B-B138A3256B7B}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.36328125" customWidth="1"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="18.7265625" customWidth="1"/>
     <col min="4" max="4" width="14.453125" customWidth="1"/>
     <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.08984375" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -1134,7 +1160,7 @@
         <v>37</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -1221,10 +1247,10 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" t="s">
         <v>146</v>
-      </c>
-      <c r="J8" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1238,19 +1264,28 @@
         <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>129</v>
+        <v>148</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M9" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
@@ -1482,7 +1517,7 @@
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -1494,10 +1529,10 @@
         <v>14</v>
       </c>
       <c r="H17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1534,7 +1569,7 @@
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -1546,10 +1581,10 @@
         <v>14</v>
       </c>
       <c r="H19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -1747,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -1770,13 +1805,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>19</v>
@@ -1854,16 +1889,16 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
         <v>13</v>
@@ -1875,13 +1910,45 @@
         <v>14</v>
       </c>
       <c r="H32" t="s">
+        <v>141</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>144</v>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33">
+        <v>2018</v>
+      </c>
+      <c r="G33">
+        <v>2021</v>
+      </c>
+      <c r="H33" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1929,8 +1996,11 @@
     <hyperlink ref="J19" r:id="rId36" display="http://www.linkedin.com/in/sam-durston-812a35293" xr:uid="{41EA5EAB-1092-4025-88C2-6B68516F645F}"/>
     <hyperlink ref="J32" r:id="rId37" xr:uid="{73AD8C54-4705-40A9-9643-92FEFA8BB733}"/>
     <hyperlink ref="K32" r:id="rId38" xr:uid="{5B5AAAAF-F891-4B3C-B316-A8C75688726E}"/>
+    <hyperlink ref="J9" r:id="rId39" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.linkedin.com%2Fin%2Famber-cowans%2F&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C7460b5026881483372d408dea14a08be%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639125536507453985%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=owOoj%2BX6dIIVqmzvbwk6odnzWsn5S7FKUDMNke8%2FbQY%3D&amp;reserved=0" xr:uid="{0D7407ED-CA39-44E4-B0C1-181859B0D9F1}"/>
+    <hyperlink ref="I33" r:id="rId40" xr:uid="{550E047B-3A74-4289-80F7-152FE2CC96ED}"/>
+    <hyperlink ref="K33" r:id="rId41" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.researchgate.net%2Fprofile%2FGoncalo-Curveira-Santos&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7Caa22359e757243cb924208dea2149d24%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639126406591585183%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=dsATszQozywwp1XZVpUIKc8TxsgIEYThxM2mbt5scZM%3D&amp;reserved=0" xr:uid="{9A9CC0B6-BF43-41EA-9520-993C8DB284A6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
 </worksheet>
 </file>
--- a/individual_details.xlsx
+++ b/individual_details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\css6\Dropbox\A\ASQ\sutherlandecology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFB6168-DC07-42B4-A408-5D9ED23B3CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F742F5-7D7B-4ECC-A2C8-1A0DAB0879D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="120" windowWidth="19140" windowHeight="11175" xr2:uid="{DEC350D0-BA79-4816-9F19-79808F91A9D5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DEC350D0-BA79-4816-9F19-79808F91A9D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="180">
   <si>
     <t>Name</t>
   </si>
@@ -555,12 +555,60 @@
   <si>
     <t>PhD student, Princeton University</t>
   </si>
+  <si>
+    <t>Shinyen Chiu</t>
+  </si>
+  <si>
+    <t>University of Queensland</t>
+  </si>
+  <si>
+    <t>chiu.jpg</t>
+  </si>
+  <si>
+    <t>Investigate (1) Potentials, challenges, and ways of utilizing individual count data from camera traps, and (2) Human disturbance impacts on wildlife sociality and group sizes.</t>
+  </si>
+  <si>
+    <t>https://cbcs.centre.uq.edu.au/profile/2550/shinyen-chiu</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shinyen-chiu/</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0004-7530-5535</t>
+  </si>
+  <si>
+    <t>Developing quantitative models to evaluate the effectiveness of invasive predator removal, with the American mink invasion in Scotland as a case study, with the aim to rigorously inform management and deliver conservation evidence.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/albert-bonet-bigat%C3%A0-442662187/?skipRedirect=true</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0006-6868-923X</t>
+  </si>
+  <si>
+    <t>https://bsky.app/profile/abonetb.bsky.social</t>
+  </si>
+  <si>
+    <t>bigata.jpg</t>
+  </si>
+  <si>
+    <t>lee.jpg</t>
+  </si>
+  <si>
+    <t>The focus of my project lies in understanding how population dynamics are influenced by an elusive subpopulation known as floaters. Using statistical approaches such as Bayesian inference, the project aims to improve our understanding of undetected age classes within long-term historical datasets.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/syl9005</t>
+  </si>
+  <si>
+    <t>https://syl9005.github.io/HomelessOwls/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,13 +620,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -620,19 +661,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,1032 +1006,1064 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{562D1C5D-4376-4368-B05B-B138A3256B7B}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.7265625" style="3"/>
-    <col min="8" max="8" width="12.1796875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.6328125" customWidth="1"/>
+    <col min="9" max="15" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
         <v>2025</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>2024</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
         <v>2026</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
         <v>2022</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
         <v>2024</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
         <v>2026</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
         <v>2026</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>144</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>146</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
         <v>2022</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>147</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
         <v>2026</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>103</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
         <v>2026</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
         <v>2026</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3">
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
         <v>2025</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14">
         <v>2020</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>2026</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
         <v>2026</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16">
         <v>2026</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
         <v>2025</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" t="s">
         <v>130</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18">
         <v>2025</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>115</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" t="s">
         <v>135</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19">
         <v>2026</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" t="s">
         <v>136</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21">
+        <v>2022</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22">
+        <v>2025</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23">
+        <v>2016</v>
+      </c>
+      <c r="G23">
+        <v>2020</v>
+      </c>
+      <c r="H23" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24">
+        <v>2016</v>
+      </c>
+      <c r="G24">
+        <v>2021</v>
+      </c>
+      <c r="H24" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25">
+        <v>2022</v>
+      </c>
+      <c r="G25">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26">
+        <v>2018</v>
+      </c>
+      <c r="G26">
+        <v>2022</v>
+      </c>
+      <c r="H26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27">
+        <v>2015</v>
+      </c>
+      <c r="G27">
+        <v>2020</v>
+      </c>
+      <c r="H27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28">
+        <v>2020</v>
+      </c>
+      <c r="G28">
+        <v>2024</v>
+      </c>
+      <c r="H28" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29">
+        <v>2016</v>
+      </c>
+      <c r="G29">
+        <v>2024</v>
+      </c>
+      <c r="H29" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30">
+        <v>2018</v>
+      </c>
+      <c r="G30">
+        <v>2026</v>
+      </c>
+      <c r="H30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31">
+        <v>2017</v>
+      </c>
+      <c r="G31">
+        <v>2022</v>
+      </c>
+      <c r="H31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>2020</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s">
+        <v>140</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33">
+        <v>2018</v>
+      </c>
+      <c r="G33">
+        <v>2021</v>
+      </c>
+      <c r="H33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B34">
         <v>0</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="C34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E34" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="3">
-        <v>2016</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2020</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2016</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F34">
+        <v>2019</v>
+      </c>
+      <c r="G34">
         <v>2021</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="3">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="3">
-        <v>2022</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2018</v>
-      </c>
-      <c r="G26" s="3">
-        <v>2022</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="3">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2015</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2020</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="3">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="3">
-        <v>2020</v>
-      </c>
-      <c r="G28" s="3">
-        <v>2024</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="3">
-        <v>2016</v>
-      </c>
-      <c r="G29" s="3">
-        <v>2024</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="3">
-        <v>1</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="3">
-        <v>2018</v>
-      </c>
-      <c r="G30" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="3">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="3">
-        <v>2017</v>
-      </c>
-      <c r="G31" s="3">
-        <v>2022</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B32" s="3">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2020</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="3">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2018</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2021</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B34" s="3">
-        <v>0</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2019</v>
-      </c>
-      <c r="G34" s="3">
-        <v>2021</v>
-      </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="4" t="s">
         <v>157</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2009,6 +2077,41 @@
       </c>
       <c r="L34" s="1" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35">
+        <v>2025</v>
+      </c>
+      <c r="G35">
+        <v>2029</v>
+      </c>
+      <c r="H35" t="s">
+        <v>167</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="O35" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2033,7 +2136,7 @@
     <hyperlink ref="K5" r:id="rId13" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.researchgate.net%2Fprofile%2FGeorgina_Whittome&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C7091bab856c44c54d69308de9713adb4%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639114307942852137%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=TDzQ%2FCz6ouLtEQYcwrtFG3Zh9eZRBRkzvtcVg7Kgj20%3D&amp;reserved=0" xr:uid="{60851D99-8B4F-4A0E-8531-9A9D4CCEC137}"/>
     <hyperlink ref="J16" r:id="rId14" display="https://eur01.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.linkedin.com%2Fin%2Fmorgan-moutte-67279b1bb&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C27aab0562cc8444bdea408de98c9e9f0%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639116190165272481%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=j7U1RKxM4A3%2Bj%2Bbe37nujI0eBh%2BIgQr%2BdUFtwwBRQh0%3D&amp;reserved=0" xr:uid="{294CF9F5-ABFC-4C4E-99FC-3403AE46DB8C}"/>
     <hyperlink ref="J6" r:id="rId15" display="https://eur01.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.linkedin.com%2Fin%2Fsarah-r-686b60197&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7Cde34cdd7c06e42b5740708de99511c11%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639116770851673137%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=Et738AP2xizpZTx2owfVRdz8Ovl9PyT%2BchD3%2BHgosfE%3D&amp;reserved=0" xr:uid="{751DB7DC-7CA9-4FBE-B5A7-FCC401A721D7}"/>
-    <hyperlink ref="N6" r:id="rId16" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fbsky.app%2Fprofile%2Fsarahrehman.bsky.social&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7Cde34cdd7c06e42b5740708de99511c11%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639116770851709646%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=TVD5u5gtZ1wWE5AM%2F0dXyelvhKX%2F6QA5J0VNTHFfQiA%3D&amp;reserved=0" xr:uid="{96EF6D11-BCF6-4995-99DB-01D9D6AFB577}"/>
+    <hyperlink ref="N6" r:id="rId16" xr:uid="{96EF6D11-BCF6-4995-99DB-01D9D6AFB577}"/>
     <hyperlink ref="J15" r:id="rId17" xr:uid="{852A7C82-1D3A-4260-80A9-732E80FBF941}"/>
     <hyperlink ref="I27" r:id="rId18" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Feos.unh.edu%2Fperson%2Falexej-siren&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C583df340090340f7e89f08de931afbad%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639109941309363181%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=uvUfRO6kAZlW6vA74tQoodEL63Ty89viw6PUI4CrUUw%3D&amp;reserved=0" xr:uid="{58900E52-D4DA-4D98-8573-C0F1846258B6}"/>
     <hyperlink ref="I23" r:id="rId19" display="https://eur01.safelinks.protection.outlook.com/?url=http%3A%2F%2Fwww.padilla-wildlife.weebly.com%2F&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C6e266bbc097a49b0350608de94bb8200%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639111730241358307%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=hiUZt%2B%2B%2FPjJ1e8UuGjgARjS6u419xB8sGABcpDW6DeE%3D&amp;reserved=0" xr:uid="{A6FDD1A5-9ED3-46C1-889B-7741960B5D70}"/>
@@ -2063,8 +2166,15 @@
     <hyperlink ref="J34" r:id="rId43" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.linkedin.com%2Fin%2Fgatesdupont%2F&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C5241127fc9b441f8f62408dea47ee15f%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639129062085005706%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=ofZrMC%2BPfwxY6Dq0rLXsvdupIyG99sP5luLhOEKjU4E%3D&amp;reserved=0" xr:uid="{98685D7C-0F4C-463B-8A95-D660BABA000F}"/>
     <hyperlink ref="K34" r:id="rId44" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.researchgate.net%2Fprofile%2FGates-Dupont&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C5241127fc9b441f8f62408dea47ee15f%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639129062084984410%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=TjEUZaAjstADxev5QIks1geySXgMpbv9lDW3CJyWIKg%3D&amp;reserved=0" xr:uid="{EF27A2A0-0598-4795-B5D0-D159EF6DB316}"/>
     <hyperlink ref="L34" r:id="rId45" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fscholar.google.com%2Fcitations%3Fuser%3DOTMAruAAAAAJ%26hl%3Den%26oi%3Dao&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C5241127fc9b441f8f62408dea47ee15f%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639129062084962241%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=yOWyRPQNAesIwMT5Z2z1YJdh4BBCaGIpkVdQplkuRCo%3D&amp;reserved=0" xr:uid="{1C60DA3C-8849-4055-B904-52D7764AF5DB}"/>
+    <hyperlink ref="I35" r:id="rId46" xr:uid="{E154F48A-5394-4F0A-9B33-FEB2A7A637C4}"/>
+    <hyperlink ref="J35" r:id="rId47" xr:uid="{F5D0EC4F-4DB8-46DE-924F-4DC2514C6978}"/>
+    <hyperlink ref="J21" r:id="rId48" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.linkedin.com%2Fin%2Falbert-bonet-bigat%25C3%25A0-442662187%2F%3FskipRedirect%3Dtrue&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C458854e1921b451dbaf908deac160add%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639137407890095042%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=vW24td4gxuczWZLSR6dDTSIX6faDwJsys7wN9UjRz4Y%3D&amp;reserved=0" xr:uid="{51F2E2B6-E07A-40EA-9668-E9B0FFCCC5E1}"/>
+    <hyperlink ref="O21" r:id="rId49" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Forcid.org%2F0009-0006-6868-923X&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C458854e1921b451dbaf908deac160add%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639137407890069083%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=2JTQdlQJunSp61IsH5RF1R6N1y%2BpKjYN8u12fsMPJ3w%3D&amp;reserved=0" xr:uid="{9645BDAD-10BC-48CC-88C5-C715966431B5}"/>
+    <hyperlink ref="N21" r:id="rId50" xr:uid="{98584A34-7C36-4992-B351-3E4918B03AA9}"/>
+    <hyperlink ref="J22" r:id="rId51" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.linkedin.com%2Fin%2Fsyl9005%3Futm_source%3Dshare_via%26utm_content%3Dprofile%26utm_medium%3Dmember_ios&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C4c3a7421d4ca48459c0508deaec71b7c%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639140367407757445%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=AO5DrXrKQzWcH2rKClE%2B6btyKEU7nXGwwY6VS%2BSRYXk%3D&amp;reserved=0" xr:uid="{40D9A0DA-51C1-4E62-BC2F-CCAC0B072997}"/>
+    <hyperlink ref="I22" r:id="rId52" display="https://eur01.safelinks.protection.outlook.com/?url=https%3A%2F%2Fsyl9005.github.io%2FHomelessOwls%2F&amp;data=05%7C02%7Ccss6%40st-andrews.ac.uk%7C4c3a7421d4ca48459c0508deaec71b7c%7Cf85626cb0da849d3aa5864ef678ef01a%7C0%7C0%7C639140367407788216%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=egGEEv1K2BWi7aoSL7pyLJAkZkM0EQqq94NdNiyAMVY%3D&amp;reserved=0" xr:uid="{9D9F67CD-BEA9-40DE-AC0B-E91D282DC4CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>